--- a/fonte/change_category.xlsx
+++ b/fonte/change_category.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projetos\symrise\fonte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14831DBD-CEFA-4DAE-B07C-115F15D03A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ECE3EB-37FC-42EF-BA14-3327290378E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2024'!$A$1:$C$545</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025'!$A$1:$K$639</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025'!$A$1:$I$639</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6172" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6155" uniqueCount="1509">
   <si>
     <t>categoria</t>
   </si>
@@ -4552,13 +4552,22 @@
     <t>Classificação_nova</t>
   </si>
   <si>
-    <t>valor_ref</t>
-  </si>
-  <si>
     <t>Classificação_atual</t>
   </si>
   <si>
-    <t>Cód. Novo (mantém antiga)</t>
+    <t>hasChanged</t>
+  </si>
+  <si>
+    <t>IgnoreAtAll</t>
+  </si>
+  <si>
+    <t>ExtendCategory</t>
+  </si>
+  <si>
+    <t>Submarca, Variante</t>
+  </si>
+  <si>
+    <t>Marca, Sub marca</t>
   </si>
 </sst>
 </file>
@@ -4620,7 +4629,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4675,18 +4684,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -4709,7 +4706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4738,19 +4735,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11038,45 +11028,45 @@
     <col min="6" max="6" width="11.875" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.25" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="10" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>553</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="14" t="s">
         <v>554</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="14" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>1502</v>
+      </c>
+      <c r="I1" s="17" t="s">
         <v>1504</v>
       </c>
-      <c r="F1" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>1502</v>
-      </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="17" t="s">
         <v>1505</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>1503</v>
+      <c r="K1" s="17" t="s">
+        <v>1506</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -11792,7 +11782,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:11">
       <c r="A33" s="11" t="s">
         <v>558</v>
       </c>
@@ -11815,7 +11805,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:11">
       <c r="A34" s="11" t="s">
         <v>558</v>
       </c>
@@ -11838,7 +11828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:11">
       <c r="A35" s="11" t="s">
         <v>558</v>
       </c>
@@ -11861,7 +11851,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:11">
       <c r="A36" s="11" t="s">
         <v>558</v>
       </c>
@@ -11884,7 +11874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:11">
       <c r="A37" s="11" t="s">
         <v>558</v>
       </c>
@@ -11907,7 +11897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:11">
       <c r="A38" s="11" t="s">
         <v>558</v>
       </c>
@@ -11930,7 +11920,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:11">
       <c r="A39" s="11" t="s">
         <v>558</v>
       </c>
@@ -11953,7 +11943,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:11">
       <c r="A40" s="11" t="s">
         <v>558</v>
       </c>
@@ -11976,7 +11966,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:11">
       <c r="A41" s="11" t="s">
         <v>558</v>
       </c>
@@ -11999,7 +11989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:11">
       <c r="A42" s="11" t="s">
         <v>558</v>
       </c>
@@ -12022,7 +12012,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:11">
       <c r="A43" s="11" t="s">
         <v>558</v>
       </c>
@@ -12045,7 +12035,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:11">
       <c r="A44" s="11" t="s">
         <v>558</v>
       </c>
@@ -12068,7 +12058,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:11">
       <c r="A45" s="11" t="s">
         <v>558</v>
       </c>
@@ -12091,7 +12081,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:11">
       <c r="A46" s="11" t="s">
         <v>558</v>
       </c>
@@ -12113,8 +12103,11 @@
       <c r="G46" s="10" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="K46" s="10" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="11" t="s">
         <v>558</v>
       </c>
@@ -12137,7 +12130,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:11">
       <c r="A48" s="11" t="s">
         <v>558</v>
       </c>
@@ -12160,7 +12153,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:11">
       <c r="A49" s="11" t="s">
         <v>558</v>
       </c>
@@ -12183,7 +12176,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:11">
       <c r="A50" s="11" t="s">
         <v>558</v>
       </c>
@@ -12206,7 +12199,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:11">
       <c r="A51" s="11" t="s">
         <v>558</v>
       </c>
@@ -12229,7 +12222,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:11">
       <c r="A52" s="11" t="s">
         <v>558</v>
       </c>
@@ -12252,7 +12245,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:11">
       <c r="A53" s="11" t="s">
         <v>558</v>
       </c>
@@ -12275,7 +12268,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:11">
       <c r="A54" s="11" t="s">
         <v>558</v>
       </c>
@@ -12298,7 +12291,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:11">
       <c r="A55" s="11" t="s">
         <v>558</v>
       </c>
@@ -12320,8 +12313,11 @@
       <c r="G55" s="10" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="K55" s="10" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="11" t="s">
         <v>558</v>
       </c>
@@ -12343,8 +12339,11 @@
       <c r="G56" s="10" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="K56" s="10" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="11" t="s">
         <v>558</v>
       </c>
@@ -12366,8 +12365,11 @@
       <c r="G57" s="10" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="K57" s="10" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="11" t="s">
         <v>558</v>
       </c>
@@ -12390,7 +12392,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:11">
       <c r="A59" s="11" t="s">
         <v>558</v>
       </c>
@@ -12413,7 +12415,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:11">
       <c r="A60" s="11" t="s">
         <v>558</v>
       </c>
@@ -12436,7 +12438,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:11">
       <c r="A61" s="11" t="s">
         <v>558</v>
       </c>
@@ -12459,7 +12461,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:11">
       <c r="A62" s="11" t="s">
         <v>558</v>
       </c>
@@ -12482,7 +12484,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:11">
       <c r="A63" s="11" t="s">
         <v>558</v>
       </c>
@@ -12505,7 +12507,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:11">
       <c r="A64" s="11" t="s">
         <v>558</v>
       </c>
@@ -14000,7 +14002,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:10">
       <c r="A129" s="11" t="s">
         <v>558</v>
       </c>
@@ -14023,7 +14025,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:10">
       <c r="A130" s="11" t="s">
         <v>558</v>
       </c>
@@ -14046,7 +14048,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:10">
       <c r="A131" s="11" t="s">
         <v>558</v>
       </c>
@@ -14069,7 +14071,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:10">
       <c r="A132" s="11" t="s">
         <v>558</v>
       </c>
@@ -14092,7 +14094,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:10">
       <c r="A133" s="11" t="s">
         <v>558</v>
       </c>
@@ -14115,7 +14117,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:10">
       <c r="A134" s="11" t="s">
         <v>558</v>
       </c>
@@ -14138,7 +14140,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:10">
       <c r="A135" s="11" t="s">
         <v>558</v>
       </c>
@@ -14161,7 +14163,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:10">
       <c r="A136" s="11" t="s">
         <v>558</v>
       </c>
@@ -14184,7 +14186,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:10">
       <c r="A137" s="11" t="s">
         <v>558</v>
       </c>
@@ -14207,7 +14209,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:10">
       <c r="A138" s="11" t="s">
         <v>558</v>
       </c>
@@ -14230,7 +14232,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:10">
       <c r="A139" s="11" t="s">
         <v>558</v>
       </c>
@@ -14253,7 +14255,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:10">
       <c r="A140" s="11" t="s">
         <v>558</v>
       </c>
@@ -14276,7 +14278,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:10">
       <c r="A141" s="11" t="s">
         <v>558</v>
       </c>
@@ -14298,8 +14300,17 @@
       <c r="G141" s="10" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="I141" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142" s="11" t="s">
         <v>558</v>
       </c>
@@ -14321,8 +14332,14 @@
       <c r="G142" s="10" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="I142" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="11" t="s">
         <v>558</v>
       </c>
@@ -14344,8 +14361,14 @@
       <c r="G143" s="10" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="I143" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="11" t="s">
         <v>558</v>
       </c>
@@ -15840,7 +15863,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:10">
       <c r="A209" s="11" t="s">
         <v>558</v>
       </c>
@@ -15863,7 +15886,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:10">
       <c r="A210" s="11" t="s">
         <v>558</v>
       </c>
@@ -15886,7 +15909,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:10">
       <c r="A211" s="11" t="s">
         <v>558</v>
       </c>
@@ -15909,7 +15932,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:10">
       <c r="A212" s="11" t="s">
         <v>558</v>
       </c>
@@ -15932,7 +15955,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:10">
       <c r="A213" s="11" t="s">
         <v>558</v>
       </c>
@@ -15955,7 +15978,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:10">
       <c r="A214" s="11" t="s">
         <v>558</v>
       </c>
@@ -15978,7 +16001,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:10">
       <c r="A215" s="11" t="s">
         <v>558</v>
       </c>
@@ -16001,7 +16024,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:10">
       <c r="A216" s="11" t="s">
         <v>558</v>
       </c>
@@ -16024,7 +16047,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:10">
       <c r="A217" s="11" t="s">
         <v>558</v>
       </c>
@@ -16047,7 +16070,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:10">
       <c r="A218" s="11" t="s">
         <v>558</v>
       </c>
@@ -16070,7 +16093,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:10">
       <c r="A219" s="11" t="s">
         <v>558</v>
       </c>
@@ -16093,7 +16116,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:10">
       <c r="A220" s="11" t="s">
         <v>558</v>
       </c>
@@ -16116,7 +16139,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:10">
       <c r="A221" s="11" t="s">
         <v>558</v>
       </c>
@@ -16129,816 +16152,669 @@
       <c r="D221" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="E221" s="25" t="s">
+      <c r="E221" s="18" t="s">
         <v>673</v>
       </c>
-      <c r="F221" s="26" t="s">
+      <c r="F221" s="19" t="s">
         <v>909</v>
       </c>
-      <c r="G221" s="25" t="s">
+      <c r="G221" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="H221" s="25" t="s">
+      <c r="H221" s="18" t="s">
         <v>555</v>
       </c>
-      <c r="I221" s="26" t="s">
-        <v>909</v>
-      </c>
-      <c r="J221" s="25" t="s">
+      <c r="I221" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J221" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B222" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E222" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F222" s="19" t="s">
+        <v>910</v>
+      </c>
+      <c r="G222" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="H222" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="I222" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E223" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F223" s="19" t="s">
+        <v>911</v>
+      </c>
+      <c r="G223" s="18" t="s">
+        <v>912</v>
+      </c>
+      <c r="H223" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="I223" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B224" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C224" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E224" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F224" s="19" t="s">
+        <v>913</v>
+      </c>
+      <c r="G224" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="H224" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I224" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C225" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E225" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F225" s="19" t="s">
+        <v>915</v>
+      </c>
+      <c r="G225" s="18" t="s">
+        <v>916</v>
+      </c>
+      <c r="H225" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I225" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B226" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D226" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E226" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F226" s="19" t="s">
+        <v>917</v>
+      </c>
+      <c r="G226" s="18" t="s">
+        <v>918</v>
+      </c>
+      <c r="H226" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I226" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B227" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C227" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E227" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F227" s="19" t="s">
+        <v>919</v>
+      </c>
+      <c r="G227" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H227" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I227" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B228" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E228" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F228" s="19" t="s">
+        <v>920</v>
+      </c>
+      <c r="G228" s="18" t="s">
+        <v>921</v>
+      </c>
+      <c r="H228" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I228" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B229" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C229" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E229" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F229" s="19" t="s">
+        <v>922</v>
+      </c>
+      <c r="G229" s="18" t="s">
+        <v>923</v>
+      </c>
+      <c r="H229" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I229" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B230" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E230" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F230" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="G230" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="H230" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I230" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B231" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C231" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D231" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E231" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F231" s="19" t="s">
+        <v>926</v>
+      </c>
+      <c r="G231" s="18" t="s">
+        <v>927</v>
+      </c>
+      <c r="H231" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I231" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B232" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C232" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D232" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E232" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F232" s="19" t="s">
+        <v>928</v>
+      </c>
+      <c r="G232" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="H232" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I232" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B233" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C233" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E233" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F233" s="19" t="s">
+        <v>930</v>
+      </c>
+      <c r="G233" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="H233" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I233" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B234" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D234" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E234" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F234" s="19" t="s">
+        <v>932</v>
+      </c>
+      <c r="G234" s="18" t="s">
+        <v>933</v>
+      </c>
+      <c r="H234" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I234" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B235" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E235" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="F235" s="19" t="s">
+        <v>934</v>
+      </c>
+      <c r="G235" s="18" t="s">
+        <v>935</v>
+      </c>
+      <c r="H235" s="18"/>
+      <c r="I235" s="18"/>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D236" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E236" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="F236" s="19" t="s">
+        <v>936</v>
+      </c>
+      <c r="G236" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H236" s="18"/>
+      <c r="I236" s="18"/>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B237" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C237" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E237" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F237" s="19" t="s">
+        <v>937</v>
+      </c>
+      <c r="G237" s="18" t="s">
+        <v>938</v>
+      </c>
+      <c r="H237" s="18"/>
+      <c r="I237" s="18"/>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B238" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D238" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E238" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F238" s="19" t="s">
+        <v>939</v>
+      </c>
+      <c r="G238" s="18" t="s">
+        <v>940</v>
+      </c>
+      <c r="H238" s="18"/>
+      <c r="I238" s="18"/>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C239" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E239" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F239" s="19" t="s">
+        <v>941</v>
+      </c>
+      <c r="G239" s="18" t="s">
+        <v>942</v>
+      </c>
+      <c r="H239" s="18"/>
+      <c r="I239" s="18"/>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E240" s="18" t="s">
+        <v>705</v>
+      </c>
+      <c r="F240" s="19" t="s">
+        <v>943</v>
+      </c>
+      <c r="G240" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="H240" s="18"/>
+      <c r="I240" s="18"/>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B241" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C241" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D241" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E241" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="F241" s="19" t="s">
+        <v>944</v>
+      </c>
+      <c r="G241" s="18" t="s">
+        <v>945</v>
+      </c>
+      <c r="H241" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="I241" s="18" t="s">
         <v>1501</v>
       </c>
-      <c r="K221" s="25">
-        <v>500368</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11">
-      <c r="A222" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B222" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C222" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D222" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E222" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="F222" s="17" t="s">
-        <v>910</v>
-      </c>
-      <c r="G222" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="H222" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="I222" s="17" t="s">
-        <v>909</v>
-      </c>
-      <c r="J222" s="16" t="s">
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B242" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D242" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E242" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F242" s="19" t="s">
+        <v>946</v>
+      </c>
+      <c r="G242" s="18" t="s">
+        <v>947</v>
+      </c>
+      <c r="H242" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I242" s="18" t="s">
         <v>1501</v>
       </c>
-      <c r="K222" s="16">
-        <v>18782</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11">
-      <c r="A223" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B223" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C223" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D223" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E223" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="F223" s="17" t="s">
-        <v>911</v>
-      </c>
-      <c r="G223" s="16" t="s">
-        <v>912</v>
-      </c>
-      <c r="H223" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="I223" s="17" t="s">
-        <v>911</v>
-      </c>
-      <c r="J223" s="16" t="s">
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B243" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C243" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D243" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E243" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F243" s="19" t="s">
+        <v>948</v>
+      </c>
+      <c r="G243" s="18" t="s">
+        <v>949</v>
+      </c>
+      <c r="H243" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I243" s="18" t="s">
         <v>1501</v>
       </c>
-      <c r="K223" s="16">
-        <v>359136</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11">
-      <c r="A224" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B224" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C224" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D224" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E224" s="14" t="s">
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B244" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D244" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E244" s="18" t="s">
         <v>780</v>
       </c>
-      <c r="F224" s="15" t="s">
-        <v>913</v>
-      </c>
-      <c r="G224" s="14" t="s">
-        <v>914</v>
-      </c>
-      <c r="H224" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I224" s="15" t="s">
-        <v>913</v>
-      </c>
-      <c r="J224" s="14" t="s">
+      <c r="F244" s="19" t="s">
+        <v>950</v>
+      </c>
+      <c r="G244" s="18" t="s">
+        <v>951</v>
+      </c>
+      <c r="H244" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="I244" s="18" t="s">
         <v>1501</v>
       </c>
-      <c r="K224" s="14">
-        <v>199834</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11">
-      <c r="A225" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B225" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C225" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D225" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E225" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F225" s="15" t="s">
-        <v>915</v>
-      </c>
-      <c r="G225" s="14" t="s">
-        <v>916</v>
-      </c>
-      <c r="H225" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I225" s="15" t="s">
-        <v>915</v>
-      </c>
-      <c r="J225" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K225" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11">
-      <c r="A226" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B226" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C226" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D226" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E226" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F226" s="15" t="s">
-        <v>917</v>
-      </c>
-      <c r="G226" s="14" t="s">
-        <v>918</v>
-      </c>
-      <c r="H226" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I226" s="15" t="s">
-        <v>917</v>
-      </c>
-      <c r="J226" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K226" s="14">
-        <v>5549</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11">
-      <c r="A227" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B227" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C227" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D227" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E227" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F227" s="15" t="s">
-        <v>919</v>
-      </c>
-      <c r="G227" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="H227" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I227" s="15" t="s">
-        <v>919</v>
-      </c>
-      <c r="J227" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K227" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11">
-      <c r="A228" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B228" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C228" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D228" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E228" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F228" s="15" t="s">
-        <v>920</v>
-      </c>
-      <c r="G228" s="14" t="s">
-        <v>921</v>
-      </c>
-      <c r="H228" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I228" s="15" t="s">
-        <v>920</v>
-      </c>
-      <c r="J228" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K228" s="14">
-        <v>74660</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11">
-      <c r="A229" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B229" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C229" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D229" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E229" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F229" s="15" t="s">
-        <v>922</v>
-      </c>
-      <c r="G229" s="14" t="s">
-        <v>923</v>
-      </c>
-      <c r="H229" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I229" s="15" t="s">
-        <v>922</v>
-      </c>
-      <c r="J229" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K229" s="14">
-        <v>34992</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11">
-      <c r="A230" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B230" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C230" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D230" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E230" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F230" s="15" t="s">
-        <v>924</v>
-      </c>
-      <c r="G230" s="14" t="s">
-        <v>925</v>
-      </c>
-      <c r="H230" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I230" s="15" t="s">
-        <v>924</v>
-      </c>
-      <c r="J230" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K230" s="14">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11">
-      <c r="A231" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B231" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C231" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D231" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E231" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F231" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="G231" s="14" t="s">
-        <v>927</v>
-      </c>
-      <c r="H231" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I231" s="15" t="s">
-        <v>926</v>
-      </c>
-      <c r="J231" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K231" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11">
-      <c r="A232" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B232" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C232" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D232" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E232" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F232" s="15" t="s">
-        <v>928</v>
-      </c>
-      <c r="G232" s="14" t="s">
-        <v>929</v>
-      </c>
-      <c r="H232" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I232" s="15" t="s">
-        <v>928</v>
-      </c>
-      <c r="J232" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K232" s="14">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11">
-      <c r="A233" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C233" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D233" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E233" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F233" s="15" t="s">
-        <v>930</v>
-      </c>
-      <c r="G233" s="14" t="s">
-        <v>931</v>
-      </c>
-      <c r="H233" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I233" s="15" t="s">
-        <v>930</v>
-      </c>
-      <c r="J233" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K233" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11">
-      <c r="A234" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B234" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C234" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D234" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E234" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F234" s="15" t="s">
-        <v>932</v>
-      </c>
-      <c r="G234" s="14" t="s">
-        <v>933</v>
-      </c>
-      <c r="H234" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I234" s="15" t="s">
-        <v>932</v>
-      </c>
-      <c r="J234" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K234" s="14">
-        <v>30388</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11">
-      <c r="A235" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B235" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C235" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D235" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E235" s="16" t="s">
-        <v>785</v>
-      </c>
-      <c r="F235" s="17" t="s">
-        <v>934</v>
-      </c>
-      <c r="G235" s="16" t="s">
-        <v>935</v>
-      </c>
-      <c r="H235" s="16" t="s">
-        <v>785</v>
-      </c>
-      <c r="I235" s="17" t="s">
-        <v>934</v>
-      </c>
-      <c r="J235" s="16"/>
-      <c r="K235" s="16">
-        <v>12440</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11">
-      <c r="A236" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B236" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C236" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D236" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E236" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="F236" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="G236" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="H236" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="I236" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="J236" s="16"/>
-      <c r="K236" s="16">
-        <v>4508</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11">
-      <c r="A237" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B237" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C237" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D237" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E237" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="F237" s="24" t="s">
-        <v>937</v>
-      </c>
-      <c r="G237" s="23" t="s">
-        <v>938</v>
-      </c>
-      <c r="H237" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="I237" s="24" t="s">
-        <v>937</v>
-      </c>
-      <c r="J237" s="23"/>
-      <c r="K237" s="23"/>
-    </row>
-    <row r="238" spans="1:11">
-      <c r="A238" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B238" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C238" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D238" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E238" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="F238" s="24" t="s">
-        <v>939</v>
-      </c>
-      <c r="G238" s="23" t="s">
-        <v>940</v>
-      </c>
-      <c r="H238" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="I238" s="24" t="s">
-        <v>939</v>
-      </c>
-      <c r="J238" s="23"/>
-      <c r="K238" s="23"/>
-    </row>
-    <row r="239" spans="1:11">
-      <c r="A239" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C239" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D239" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E239" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="F239" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="G239" s="23" t="s">
-        <v>942</v>
-      </c>
-      <c r="H239" s="23" t="s">
-        <v>669</v>
-      </c>
-      <c r="I239" s="24" t="s">
-        <v>941</v>
-      </c>
-      <c r="J239" s="23"/>
-      <c r="K239" s="23"/>
-    </row>
-    <row r="240" spans="1:11">
-      <c r="A240" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B240" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C240" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D240" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E240" s="16" t="s">
-        <v>705</v>
-      </c>
-      <c r="F240" s="17" t="s">
-        <v>943</v>
-      </c>
-      <c r="G240" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="H240" s="16" t="s">
-        <v>705</v>
-      </c>
-      <c r="I240" s="16" t="s">
-        <v>943</v>
-      </c>
-      <c r="J240" s="16"/>
-      <c r="K240" s="16">
-        <v>115368</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11">
-      <c r="A241" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B241" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C241" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E241" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="F241" s="17" t="s">
-        <v>944</v>
-      </c>
-      <c r="G241" s="16" t="s">
-        <v>945</v>
-      </c>
-      <c r="H241" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="I241" s="16" t="s">
-        <v>944</v>
-      </c>
-      <c r="J241" s="16" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K241" s="16">
-        <v>2574</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11">
-      <c r="A242" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B242" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C242" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D242" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E242" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F242" s="15" t="s">
-        <v>946</v>
-      </c>
-      <c r="G242" s="14" t="s">
-        <v>947</v>
-      </c>
-      <c r="H242" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I242" s="14" t="s">
-        <v>946</v>
-      </c>
-      <c r="J242" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K242" s="14">
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="243" spans="1:11">
-      <c r="A243" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B243" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C243" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D243" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E243" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F243" s="15" t="s">
-        <v>948</v>
-      </c>
-      <c r="G243" s="14" t="s">
-        <v>949</v>
-      </c>
-      <c r="H243" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I243" s="14" t="s">
-        <v>948</v>
-      </c>
-      <c r="J243" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K243" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11">
-      <c r="A244" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B244" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C244" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D244" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="E244" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="F244" s="15" t="s">
-        <v>950</v>
-      </c>
-      <c r="G244" s="14" t="s">
-        <v>951</v>
-      </c>
-      <c r="H244" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="I244" s="14" t="s">
-        <v>950</v>
-      </c>
-      <c r="J244" s="14" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K244" s="14">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11">
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245" s="11" t="s">
         <v>558</v>
       </c>
@@ -16961,7 +16837,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:9">
       <c r="A246" s="11" t="s">
         <v>558</v>
       </c>
@@ -16984,7 +16860,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:9">
       <c r="A247" s="11" t="s">
         <v>558</v>
       </c>
@@ -17007,7 +16883,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:9">
       <c r="A248" s="11" t="s">
         <v>558</v>
       </c>
@@ -17030,7 +16906,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:9">
       <c r="A249" s="11" t="s">
         <v>558</v>
       </c>
@@ -17053,7 +16929,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:9">
       <c r="A250" s="11" t="s">
         <v>558</v>
       </c>
@@ -17076,7 +16952,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:9">
       <c r="A251" s="11" t="s">
         <v>558</v>
       </c>
@@ -17099,7 +16975,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:9">
       <c r="A252" s="11" t="s">
         <v>558</v>
       </c>
@@ -17122,7 +16998,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:9">
       <c r="A253" s="11" t="s">
         <v>558</v>
       </c>
@@ -17145,7 +17021,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:9">
       <c r="A254" s="11" t="s">
         <v>558</v>
       </c>
@@ -17168,7 +17044,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:9">
       <c r="A255" s="11" t="s">
         <v>558</v>
       </c>
@@ -17191,7 +17067,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:9">
       <c r="A256" s="11" t="s">
         <v>558</v>
       </c>
@@ -20158,7 +20034,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:11">
       <c r="A385" s="11" t="s">
         <v>558</v>
       </c>
@@ -20181,7 +20057,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:11">
       <c r="A386" s="11" t="s">
         <v>558</v>
       </c>
@@ -20204,7 +20080,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:11">
       <c r="A387" s="11" t="s">
         <v>558</v>
       </c>
@@ -20227,7 +20103,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:11">
       <c r="A388" s="11" t="s">
         <v>558</v>
       </c>
@@ -20250,7 +20126,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:11">
       <c r="A389" s="11" t="s">
         <v>558</v>
       </c>
@@ -20273,7 +20149,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:11">
       <c r="A390" s="11" t="s">
         <v>558</v>
       </c>
@@ -20296,7 +20172,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:11">
       <c r="A391" s="11" t="s">
         <v>558</v>
       </c>
@@ -20319,7 +20195,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:11">
       <c r="A392" s="11" t="s">
         <v>558</v>
       </c>
@@ -20342,7 +20218,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:11">
       <c r="A393" s="11" t="s">
         <v>558</v>
       </c>
@@ -20365,7 +20241,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:11">
       <c r="A394" s="11" t="s">
         <v>558</v>
       </c>
@@ -20387,8 +20263,11 @@
       <c r="G394" s="10" t="s">
         <v>1173</v>
       </c>
-    </row>
-    <row r="395" spans="1:7">
+      <c r="K394" s="10" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11">
       <c r="A395" s="11" t="s">
         <v>558</v>
       </c>
@@ -20411,7 +20290,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:11">
       <c r="A396" s="11" t="s">
         <v>558</v>
       </c>
@@ -20434,7 +20313,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:11">
       <c r="A397" s="11" t="s">
         <v>558</v>
       </c>
@@ -20457,7 +20336,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:11">
       <c r="A398" s="11" t="s">
         <v>558</v>
       </c>
@@ -20480,7 +20359,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:11">
       <c r="A399" s="11" t="s">
         <v>558</v>
       </c>
@@ -20503,7 +20382,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:11">
       <c r="A400" s="11" t="s">
         <v>558</v>
       </c>
@@ -26024,7 +25903,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K639" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
